--- a/Scripts4Scripps.suite/Resources/ConsentForms.xlsx
+++ b/Scripts4Scripps.suite/Resources/ConsentForms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ScriptRepositories\Scripps\Scripts4Scripps.suite\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E63ABE-58C9-4995-8EC8-067651DB4666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217DE82F-BE3D-46DB-BFC6-E929C222B254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{C864BDB0-4385-4BB3-84E1-4F66A64FF911}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
   <si>
     <t>PatientFirstName</t>
   </si>
@@ -50,12 +50,6 @@
     <t>ProviderNameAndTitle</t>
   </si>
   <si>
-    <t>ProcedureTitle</t>
-  </si>
-  <si>
-    <t>ProcedureSubtitle</t>
-  </si>
-  <si>
     <t>ProcedureDate</t>
   </si>
   <si>
@@ -249,6 +243,21 @@
   </si>
   <si>
     <t>&lt;NONE&gt; VASCULARIZED LYMPH NODE TRANSFER</t>
+  </si>
+  <si>
+    <t>ProcedureTitle1</t>
+  </si>
+  <si>
+    <t>ProcedureSubtitle2</t>
+  </si>
+  <si>
+    <t>ProcedureSubtitle1</t>
+  </si>
+  <si>
+    <t>ProcedureTitle2</t>
+  </si>
+  <si>
+    <t>(A surgery to improve the cosmetic appearance of my abdomen by suctioning excess fat from under the surface of the skin using the ultrasonic technique.)</t>
   </si>
 </sst>
 </file>
@@ -324,7 +333,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -333,6 +342,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -669,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884CFEE1-91C8-4AEE-9B18-64D71F1CC7D3}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" bestFit="1" customWidth="1"/>
@@ -679,11 +694,13 @@
     <col min="5" max="5" width="14.81640625" customWidth="1"/>
     <col min="6" max="6" width="48.6328125" customWidth="1"/>
     <col min="7" max="7" width="125.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.6328125" customWidth="1"/>
+    <col min="9" max="9" width="125.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,283 +711,317 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
         <v>59</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F7" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D8" t="s">
+        <v>64</v>
+      </c>
+      <c r="E8" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F8" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="F9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B10" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s">
         <v>62</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" t="s">
         <v>63</v>
       </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="F11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="H12" s="2"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J12" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
